--- a/main/ig/mappingPriseEnchargeCDAFHIR.xlsx
+++ b/main/ig/mappingPriseEnchargeCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T15:44:19+00:00</t>
+    <t>2025-08-01T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPriseEnchargeCDAFHIR.xlsx
+++ b/main/ig/mappingPriseEnchargeCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T08:11:50+00:00</t>
+    <t>2025-08-22T10:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPriseEnchargeCDAFHIR.xlsx
+++ b/main/ig/mappingPriseEnchargeCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T10:16:53+00:00</t>
+    <t>2025-08-25T15:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPriseEnchargeCDAFHIR.xlsx
+++ b/main/ig/mappingPriseEnchargeCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:42:10+00:00</t>
+    <t>2025-10-02T14:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPriseEnchargeCDAFHIR.xlsx
+++ b/main/ig/mappingPriseEnchargeCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T14:05:03+00:00</t>
+    <t>2025-10-02T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPriseEnchargeCDAFHIR.xlsx
+++ b/main/ig/mappingPriseEnchargeCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T15:16:38+00:00</t>
+    <t>2025-10-13T15:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPriseEnchargeCDAFHIR.xlsx
+++ b/main/ig/mappingPriseEnchargeCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T15:21:05+00:00</t>
+    <t>2025-10-20T17:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPriseEnchargeCDAFHIR.xlsx
+++ b/main/ig/mappingPriseEnchargeCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-20T17:15:49+00:00</t>
+    <t>2025-10-21T08:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPriseEnchargeCDAFHIR.xlsx
+++ b/main/ig/mappingPriseEnchargeCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T08:14:34+00:00</t>
+    <t>2025-10-21T15:23:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPriseEnchargeCDAFHIR.xlsx
+++ b/main/ig/mappingPriseEnchargeCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T15:23:03+00:00</t>
+    <t>2025-10-21T16:49:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,16 +105,16 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/PriseEncharge</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-prise-en-charge</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-component-of</t>
-  </si>
-  <si>
-    <t>PriseEncharge</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-component-of</t>
+  </si>
+  <si>
+    <t>FRLMPriseEncharge</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -123,91 +123,91 @@
     <t>componentOf</t>
   </si>
   <si>
-    <t>PriseEncharge.identifiantPriseEnCharge</t>
+    <t>FRLMPriseEncharge.identifiantPriseEnCharge</t>
   </si>
   <si>
     <t>componentOf.encompassingEncounter.id</t>
   </si>
   <si>
-    <t>PriseEncharge.typePriseEnCharge</t>
+    <t>FRLMPriseEncharge.typePriseEnCharge</t>
   </si>
   <si>
     <t>componentOf.encompassingEncounter.code</t>
   </si>
   <si>
-    <t>PriseEncharge.dateDebutFinPriseEnCharge</t>
+    <t>FRLMPriseEncharge.dateDebutFinPriseEnCharge</t>
   </si>
   <si>
     <t>componentOf.encompassingEncounter.effectiveTime</t>
   </si>
   <si>
-    <t>PriseEncharge.typeSortie</t>
+    <t>FRLMPriseEncharge.typeSortie</t>
   </si>
   <si>
     <t>componentOf.encompassingEncounter.dischargeDispositionCode</t>
   </si>
   <si>
-    <t>PriseEncharge.responsablePriseEnCharge</t>
+    <t>FRLMPriseEncharge.responsablePriseEnCharge</t>
   </si>
   <si>
     <t>componentOf.encompassingEncounter.responsibleParty.assignedEntity</t>
   </si>
   <si>
-    <t>PriseEncharge.personneImpliqueePriseEnCharge</t>
+    <t>FRLMPriseEncharge.personneImpliqueePriseEnCharge</t>
   </si>
   <si>
     <t>componentOf.encompassingEncounter.encounterParticipant</t>
   </si>
   <si>
-    <t>PriseEncharge.personneImpliqueePriseEnCharge.typeParticipation</t>
+    <t>FRLMPriseEncharge.personneImpliqueePriseEnCharge.typeParticipation</t>
   </si>
   <si>
     <t>componentOf.encompassingEncounter.encounterParticipant@typeCode</t>
   </si>
   <si>
-    <t>PriseEncharge.personneImpliqueePriseEnCharge.dateDebutFinParticipation</t>
+    <t>FRLMPriseEncharge.personneImpliqueePriseEnCharge.dateDebutFinParticipation</t>
   </si>
   <si>
     <t>componentOf.encompassingEncounter.encounterParticipant.time</t>
   </si>
   <si>
-    <t>PriseEncharge.personneImpliqueePriseEnCharge.professionnelImplique</t>
+    <t>FRLMPriseEncharge.personneImpliqueePriseEnCharge.professionnelImplique</t>
   </si>
   <si>
     <t>componentOf.encompassingEncounter.encounterParticipant.assignedEntity</t>
   </si>
   <si>
-    <t>PriseEncharge.lieuPriseEnCharge</t>
+    <t>FRLMPriseEncharge.lieuPriseEnCharge</t>
   </si>
   <si>
     <t>componentOf.encompassingEncounter.location</t>
   </si>
   <si>
-    <t>PriseEncharge.lieuPriseEnCharge.structure</t>
+    <t>FRLMPriseEncharge.lieuPriseEnCharge.structure</t>
   </si>
   <si>
     <t>componentOf.encompassingEncounter.location.healthcareFacility</t>
   </si>
   <si>
-    <t>PriseEncharge.lieuPriseEnCharge.structure.secteurActivite</t>
+    <t>FRLMPriseEncharge.lieuPriseEnCharge.structure.secteurActivite</t>
   </si>
   <si>
     <t>componentOf.encompassingEncounter.location.healthcareFacility.code</t>
   </si>
   <si>
-    <t>PriseEncharge.lieuPriseEnCharge.structure.secteurActivite.categorieEtablissement</t>
+    <t>FRLMPriseEncharge.lieuPriseEnCharge.structure.secteurActivite.categorieEtablissement</t>
   </si>
   <si>
     <t>componentOf.encompassingEncounter.location.healthcareFacility.code.translation</t>
   </si>
   <si>
-    <t>PriseEncharge.lieuPriseEnCharge.structure.nomStructure</t>
+    <t>FRLMPriseEncharge.lieuPriseEnCharge.structure.nomStructure</t>
   </si>
   <si>
     <t>componentOf.encompassingEncounter.location.healthcareFacility.location.name</t>
   </si>
   <si>
-    <t>PriseEncharge.lieuPriseEnCharge.structure.adresse</t>
+    <t>FRLMPriseEncharge.lieuPriseEnCharge.structure.adresse</t>
   </si>
   <si>
     <t>componentOf.encompassingEncounter.location.healthcareFacility.location.addr</t>

--- a/main/ig/mappingPriseEnchargeCDAFHIR.xlsx
+++ b/main/ig/mappingPriseEnchargeCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T16:49:23+00:00</t>
+    <t>2025-10-21T17:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPriseEnchargeCDAFHIR.xlsx
+++ b/main/ig/mappingPriseEnchargeCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T17:18:21+00:00</t>
+    <t>2025-10-22T08:56:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
